--- a/df_expanded.xlsx
+++ b/df_expanded.xlsx
@@ -4471,7 +4471,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB37D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB33B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3680&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB37A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB38C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB36E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB36B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB34A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7950&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7B60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7B30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F48E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7AA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7AD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7A40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C500&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C620&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C5F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C650&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C560&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C590&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C5C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C470&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C770&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C7D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C6B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C6E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C8C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C8F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C950&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C9B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C9E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CA10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CA40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CA70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CAA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CAD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CB00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CB30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CB60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CB90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CBC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CBF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CC20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CC50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CC80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CCB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CCE0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB37D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB33B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3680&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB37A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB38C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB36E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB36B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB34A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7950&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7B60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7B30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F48E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7AA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7AD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7A40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C500&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C620&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C5F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C650&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C560&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C590&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C5C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C470&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C770&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C7D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C6B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C6E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C8C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C8F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C950&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C9B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C9E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CA10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CA40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CA70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CAA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CAD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CB00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CB30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CB60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CB90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CBC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CBF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CC20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CC50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CC80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CCB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CCE0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4517,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB37D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB33B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3680&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB37A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB38C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB36E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB36B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB34A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7950&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7B60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7B30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F48E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7AA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7AD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7A40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FA7E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C500&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C620&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C5F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C650&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C560&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C590&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C5C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C470&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C770&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C7D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C6B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C6E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C8C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C8F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C950&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C9B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C9E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CA10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CA40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CA70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CAA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CAD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CB00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CB30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CB60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CB90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CBC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CBF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CC20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CC50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CC80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CCB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CCE0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C4D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CE90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CE00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CDA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C7A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C530&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CD70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CF20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CF50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CF80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CFB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CFE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D010&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D040&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D070&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D0A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D0D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D100&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D130&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D160&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D190&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D1C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D1F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D220&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D250&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D280&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D2B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D2E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D310&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D340&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D370&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D3A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D3D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D400&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D430&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D4C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D4F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D580&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D5B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D5E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D610&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D640&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D670&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D6A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D6D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D700&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D760&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D790&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D7C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D7F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D820&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D850&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D880&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D8B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D8E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D910&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D940&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D970&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D9A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D9D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DA00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DA30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DA60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DA90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DAC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DAF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DB20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DB50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DB80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DBB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DBE0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C4D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CE90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CE00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CDA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C7A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C530&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CD70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CF20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CF50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CF80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CFB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CFE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D010&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D040&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D070&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D0A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D0D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D100&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D130&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D160&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D190&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D1C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D1F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D220&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D250&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D280&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D2B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D2E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D310&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D340&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D370&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D3A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D3D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D400&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D430&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D4C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D4F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D580&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D5B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D5E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D610&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D640&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D670&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D6A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D6D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D700&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D760&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D790&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D7C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D7F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D820&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D850&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D880&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D8B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D8E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D910&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D940&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D970&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D9A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1D9D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DA00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DA30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DA60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DA90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DAC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DAF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DB20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DB50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DB80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DBB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DBE0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CEF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB39E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DD90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CE30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DD00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CEC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DCA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CD40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CDD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DE20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DE50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DE80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DEB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DEE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DF10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DF40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DF70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DFA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DFD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E000&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E030&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E060&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E090&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E0C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E0F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E120&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E150&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E180&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E1B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E1E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E210&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E240&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E270&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E2A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E2D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E300&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E330&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E360&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E390&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E3C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E3F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E420&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E450&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E480&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E4B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E4E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E510&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E540&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E570&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E5A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E5D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E600&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E630&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E660&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E690&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E6C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E6F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E720&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E750&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E780&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E7B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E7E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E810&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E840&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E870&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E8A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E8D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E900&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E930&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E960&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E990&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E9C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E9F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EA20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EA50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EA80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EAB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EAE0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CEF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB39E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DD90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CE30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DD00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CEC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DCA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CD40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CDD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DE20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DE50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DE80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DEB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DEE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DF10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DF40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DF70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DFA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DFD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E000&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E030&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E060&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E090&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E0C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E0F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E120&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E150&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E180&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E1B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E1E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E210&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E240&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E270&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E2A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E2D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E300&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E330&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E360&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E390&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E3C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E3F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E420&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E450&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E480&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E4B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E4E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E510&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E540&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E570&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E5A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E5D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E600&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E630&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E660&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E690&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E6C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E6F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E720&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E750&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E780&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E7B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E7E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E810&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E840&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E870&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E8A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E8D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E900&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E930&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E960&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E990&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E9C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E9F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EA20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EA50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EA80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EAB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EAE0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CEF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB39E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DD90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CE30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DD00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CEC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DCA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CD40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CDD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DE20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DE50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DE80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DEB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DEE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DF10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DF40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DF70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DFA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DFD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E000&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E030&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E060&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E090&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E0C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E0F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E120&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E150&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E180&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E1B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E1E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E210&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E240&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E270&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E2A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E2D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E300&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E330&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E360&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E390&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E3C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E3F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E420&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E450&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E480&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E4B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E4E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E510&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E540&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E570&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E5A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E5D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E600&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E630&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E660&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E690&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E6C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E6F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E720&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E750&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E780&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E7B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E7E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E810&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E840&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E870&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E8A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E8D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E900&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E930&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E960&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E990&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E9C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E9F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EA20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EA50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EA80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EAB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EAE0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CEF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB39E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DD90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CE30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DD00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CEC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DCA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CD40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CDD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DE20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DE50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DE80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DEB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DEE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DF10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DF40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DF70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DFA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DFD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E000&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E030&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E060&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E090&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E0C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E0F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E120&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E150&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E180&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E1B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E1E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E210&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E240&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E270&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E2A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E2D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E300&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E330&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E360&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E390&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E3C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E3F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E420&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E450&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E480&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E4B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E4E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E510&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E540&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E570&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E5A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E5D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E600&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E630&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E660&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E690&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E6C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E6F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E720&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E750&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E780&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E7B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E7E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E810&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E840&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E870&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E8A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E8D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E900&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E930&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E960&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E990&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E9C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E9F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EA20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EA50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EA80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EAB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EAE0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CEF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB39E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DD90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CE30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DD00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CEC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DCA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CD40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CDD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DE20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DE50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DE80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DEB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DEE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DF10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DF40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DF70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DFA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DFD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E000&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E030&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E060&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E090&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E0C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E0F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E120&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E150&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E180&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E1B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E1E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E210&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E240&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E270&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E2A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E2D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E300&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E330&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E360&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E390&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E3C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E3F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E420&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E450&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E480&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E4B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E4E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E510&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E540&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E570&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E5A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E5D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E600&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E630&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E660&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E690&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E6C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E6F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E720&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E750&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E780&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E7B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E7E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E810&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E840&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E870&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E8A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E8D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E900&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E930&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E960&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E990&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E9C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E9F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EA20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EA50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EA80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EAB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EAE0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CEF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB39E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DD90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CE30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DD00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CEC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DCA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CD40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CDD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DE20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DE50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DE80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DEB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DEE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DF10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DF40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DF70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DFA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DFD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E000&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E030&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E060&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E090&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E0C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E0F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E120&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E150&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E180&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E1B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E1E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E210&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E240&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E270&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E2A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E2D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E300&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E330&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E360&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E390&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E3C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E3F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E420&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E450&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E480&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E4B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E4E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E510&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E540&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E570&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E5A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E5D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E600&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E630&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E660&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E690&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E6C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E6F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E720&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E750&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E780&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E7B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E7E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E810&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E840&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E870&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E8A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E8D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E900&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E930&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E960&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E990&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E9C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1E9F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EA20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EA50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EA80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EAB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EAE0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4724,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EB40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DDF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ECC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EC90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DDC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EBA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C4A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DC40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DD60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CD10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ED20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ED50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ED80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EDB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EDE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EE10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EE40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EE70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EEA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EED0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EF00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EF30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EF60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EF90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EFC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EFF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F020&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F050&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F0B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F0E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F170&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F1A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F1D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F200&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F230&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F260&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F290&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F2C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F2F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F320&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F350&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F380&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F3B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F3E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F410&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F470&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F4A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F4D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F500&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F530&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F560&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F590&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F5C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F5F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F620&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F650&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F680&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F6B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F6E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F770&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F7A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F7D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F8C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F8F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F950&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F9B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F9E0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EB40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DDF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ECC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EC90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DDC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EBA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C4A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DC40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DD60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CD10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ED20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ED50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ED80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EDB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EDE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EE10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EE40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EE70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EEA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EED0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EF00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EF30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EF60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EF90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EFC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EFF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F020&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F050&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F0B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F0E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F170&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F1A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F1D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F200&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F230&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F260&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F290&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F2C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F2F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F320&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F350&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F380&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F3B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F3E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F410&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F470&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F4A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F4D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F500&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F530&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F560&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F590&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F5C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F5F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F620&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F650&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F680&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F6B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F6E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F770&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F7A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F7D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F8C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F8F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F950&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F9B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F9E0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EB40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DDF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ECC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EC90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DDC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EBA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C4A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DC40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DD60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CD10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ED20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ED50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ED80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EDB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EDE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EE10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EE40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EE70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EEA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EED0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EF00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EF30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EF60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EF90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EFC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EFF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F020&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F050&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F0B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F0E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F170&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F1A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F1D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F200&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F230&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F260&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F290&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F2C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F2F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F320&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F350&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F380&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F3B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F3E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F410&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F470&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F4A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F4D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F500&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F530&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F560&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F590&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F5C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F5F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F620&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F650&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F680&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F6B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F6E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F770&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F7A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F7D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F8C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F8F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F950&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F9B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F9E0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EB40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DDF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ECC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EC90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DDC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EBA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C4A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DC40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DD60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CD10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ED20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ED50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ED80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EDB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EDE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EE10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EE40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EE70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EEA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EED0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EF00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EF30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EF60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EF90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EFC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EFF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F020&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F050&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F0B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F0E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F170&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F1A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F1D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F200&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F230&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F260&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F290&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F2C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F2F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F320&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F350&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F380&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F3B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F3E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F410&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F470&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F4A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F4D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F500&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F530&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F560&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F590&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F5C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F5F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F620&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F650&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F680&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F6B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F6E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F770&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F7A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F7D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F8C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F8F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F950&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F9B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F9E0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EB40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DDF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ECC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EC90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DDC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EBA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1C4A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DC40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DD60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CD10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ED20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ED50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ED80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EDB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EDE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EE10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EE40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EE70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EEA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EED0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EF00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EF30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EF60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EF90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EFC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EFF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F020&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F050&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F0B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F0E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F170&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F1A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F1D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F200&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F230&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F260&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F290&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F2C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F2F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F320&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F350&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F380&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F3B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F3E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F410&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F470&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F4A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F4D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F500&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F530&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F560&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F590&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F5C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F5F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F620&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F650&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F680&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F6B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F6E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F770&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F7A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F7D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F8C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F8F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F950&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F9B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1F9E0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FA40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ECF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FBC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FB90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EC30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FAA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DC70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DD30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EC00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EB10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FC20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FC50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FC80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FCB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FCE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FD10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FD40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FD70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FDA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FDD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FE00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FE30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FE60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FE90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FEC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FEF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FF20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FF50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FF80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FFB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FFE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EB70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FAD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FB30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DCD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FB00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CE60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FB60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC41A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC41D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4200&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4230&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4260&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4290&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC42C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC42F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4320&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4350&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4380&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC43B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC43E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4410&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4470&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC44A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC44D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4500&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4530&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4560&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4590&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC45C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC45F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4620&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4650&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4680&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC46B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC46E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4770&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC47A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC47D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC48C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC48F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4950&gt;]}</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FA40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ECF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FBC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FB90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EC30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FAA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DC70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DD30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EC00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EB10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FC20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FC50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FC80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FCB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FCE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FD10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FD40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FD70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FDA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FDD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FE00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FE30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FE60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FE90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FEC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FEF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FF20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FF50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FF80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FFB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FFE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EB70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FAD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FB30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DCD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FB00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CE60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FB60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC41A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC41D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4200&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4230&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4260&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4290&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC42C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC42F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4320&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4350&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4380&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC43B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC43E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4410&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4470&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC44A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC44D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4500&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4530&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4560&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4590&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC45C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC45F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4620&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4650&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4680&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC46B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC46E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4770&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC47A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC47D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC48C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC48F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4950&gt;]}</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FA40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ECF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FBC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FB90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EC30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FAA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DC70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DD30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EC00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EB10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FC20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FC50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FC80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FCB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FCE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FD10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FD40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FD70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FDA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FDD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FE00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FE30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FE60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FE90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FEC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FEF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FF20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FF50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FF80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FFB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FFE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EB70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FAD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FB30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DCD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FB00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CE60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FB60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC41A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC41D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4200&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4230&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4260&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4290&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC42C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC42F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4320&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4350&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4380&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC43B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC43E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4410&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4470&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC44A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC44D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4500&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4530&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4560&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4590&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC45C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC45F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4620&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4650&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4680&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC46B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC46E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4770&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC47A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC47D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC48C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC48F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4950&gt;]}</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FA40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ECF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FBC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FB90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EC30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FAA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DC70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DD30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EC00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EB10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FC20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FC50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FC80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FCB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FCE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FD10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FD40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FD70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FDA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FDD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FE00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FE30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FE60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FE90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FEC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FEF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FF20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FF50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FF80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FFB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FFE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EB70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FAD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FB30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DCD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FB00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CE60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FB60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC41A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC41D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4200&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4230&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4260&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4290&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC42C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC42F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4320&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4350&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4380&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC43B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC43E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4410&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4470&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC44A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC44D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4500&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4530&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4560&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4590&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC45C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC45F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4620&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4650&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4680&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC46B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC46E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4770&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC47A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC47D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC48C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC48F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4950&gt;]}</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FA40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1ECF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FBC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FB90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EC30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FAA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DC70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DD30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EC00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EB10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FC20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FC50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FC80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FCB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FCE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FD10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FD40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FD70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FDA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FDD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FE00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FE30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FE60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FE90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FEC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FEF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FF20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FF50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FF80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FFB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FFE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EB70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FAD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FB30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1DCD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FB00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1CE60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FB60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC41A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC41D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4200&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4230&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4260&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4290&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC42C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC42F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4320&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4350&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4380&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC43B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC43E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4410&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4470&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC44A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC44D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4500&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4530&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4560&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4590&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC45C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC45F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4620&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4650&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4680&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC46B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC46E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4770&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC47A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC47D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC48C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC48F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4950&gt;]}</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FA70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC49E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5010&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5040&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5070&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5100&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5130&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5160&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5190&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5220&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5250&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5280&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5310&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5340&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5370&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5400&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5430&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5580&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5610&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5640&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5670&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5700&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5760&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5790&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5820&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5850&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5880&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5910&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5940&gt;]}</t>
         </is>
       </c>
     </row>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FA70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC49E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5010&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5040&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5070&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5100&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5130&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5160&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5190&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5220&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5250&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5280&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5310&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5340&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5370&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5400&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5430&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5580&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5610&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5640&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5670&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5700&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5760&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5790&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5820&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5850&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5880&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5910&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5940&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FA70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC49E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5010&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5040&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5070&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5100&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5130&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5160&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5190&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5220&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5250&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5280&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5310&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5340&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5370&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5400&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5430&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5580&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5610&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5640&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5670&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5700&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5760&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5790&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5820&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5850&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5880&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5910&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5940&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FA70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC49E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5010&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5040&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5070&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5100&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5130&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5160&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5190&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5220&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5250&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5280&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5310&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5340&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5370&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5400&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5430&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5580&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5610&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5640&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5670&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5700&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5760&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5790&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5820&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5850&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5880&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5910&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5940&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FA70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC49E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5010&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5040&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5070&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5100&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5130&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5160&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5190&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5220&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5250&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5280&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5310&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5340&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5370&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5400&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5430&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5580&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5610&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5640&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5670&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5700&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5760&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5790&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5820&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5850&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5880&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5910&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5940&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FA70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC49E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5010&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5040&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5070&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5100&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5130&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5160&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5190&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5220&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5250&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5280&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5310&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5340&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5370&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5400&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5430&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5580&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5610&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5640&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5670&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5700&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5760&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5790&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5820&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5850&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5880&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5910&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5940&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FA70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC49E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5010&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5040&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5070&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5100&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5130&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5160&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5190&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5220&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5250&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5280&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5310&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5340&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5370&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5400&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5430&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5580&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5610&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5640&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5670&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5700&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5760&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5790&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5820&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5850&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5880&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5910&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5940&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FA70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC49E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5010&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5040&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5070&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5100&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5130&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5160&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5190&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5220&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5250&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5280&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5310&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5340&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5370&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5400&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5430&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5580&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5610&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5640&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5670&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5700&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5760&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5790&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5820&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5850&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5880&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5910&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5940&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FA70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC49E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5010&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5040&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5070&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5100&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5130&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5160&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5190&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5220&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5250&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5280&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5310&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5340&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5370&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5400&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5430&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5580&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5610&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5640&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5670&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5700&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5760&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5790&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5820&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5850&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5880&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5910&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5940&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FA70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC49E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5010&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5040&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5070&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5100&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5130&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5160&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5190&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5220&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5250&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5280&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5310&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5340&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5370&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5400&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5430&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5580&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5610&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5640&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5670&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5700&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5760&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5790&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5820&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5850&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5880&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5910&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5940&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FA70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC49E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5010&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5040&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5070&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5100&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5130&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5160&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5190&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5220&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5250&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5280&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5310&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5340&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5370&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5400&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5430&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5580&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5610&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5640&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5670&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5700&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5760&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5790&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5820&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5850&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5880&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5910&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5940&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FA70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC49E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5010&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5040&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5070&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5100&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5130&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5160&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5190&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5220&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5250&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5280&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5310&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5340&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5370&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5400&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5430&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5580&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5610&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5640&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5670&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5700&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5760&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5790&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5820&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5850&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5880&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5910&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5940&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FA70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC49E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5010&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5040&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5070&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5100&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5130&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5160&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5190&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5220&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5250&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5280&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5310&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5340&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5370&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5400&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5430&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5580&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5610&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5640&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5670&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5700&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5760&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5790&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5820&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5850&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5880&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5910&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5940&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1FA70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC40B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC49E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4D70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4E90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4EF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4FE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5010&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5040&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5070&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC50D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5100&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5130&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5160&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5190&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC51F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5220&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5250&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5280&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC52E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5310&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5340&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5370&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC53D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5400&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5430&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC54F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5580&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC55E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5610&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5640&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5670&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC56D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5700&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5760&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5790&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC57F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5820&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5850&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5880&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC58E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5910&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5940&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5AF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4AD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5A60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4170&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5A00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC49B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4AA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5B80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5BB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5BE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5C10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5C40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5C70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5CA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5CD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5D00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5D30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5D60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5D90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5DC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5DF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5E20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5E50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5E80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5EB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5EE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985D06D50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB1D60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB1D30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB28D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2840&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2960&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2990&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2780&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2690&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB26C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB29C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB29F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB23F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2240&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2390&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2270&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB27B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2870&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB28A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB1D90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2660&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB1DC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2930&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79250&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F792E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79220&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79280&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F791F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F78B30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F792B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F798B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F794C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F794F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4050&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC59A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5B20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5FD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6000&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6030&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6060&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6090&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC60C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC60F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6120&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6150&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6180&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC61B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC61E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6210&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5AF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4AD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5A60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4170&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5A00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC49B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4AA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5B80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5BB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5BE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5C10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5C40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5C70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5CA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5CD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5D00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5D30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5D60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5D90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5DC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5DF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5E20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5E50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5E80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5EB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5EE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985D06D50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB1D60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB1D30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB28D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2840&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2960&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2990&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2780&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2690&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB26C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB29C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB29F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB23F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2240&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2390&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2270&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB27B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2870&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB28A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB1D90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2660&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB1DC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2930&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79250&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F792E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79220&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79280&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F791F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F78B30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F792B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F798B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F794C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F794F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4050&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC59A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5B20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5FD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6000&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6030&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6060&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6090&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC60C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC60F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6120&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6150&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6180&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC61B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC61E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6210&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5AF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4AD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5A60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4170&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5A00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC49B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4AA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5B80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5BB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5BE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5C10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5C40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5C70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5CA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5CD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5D00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5D30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5D60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5D90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5DC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5DF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5E20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5E50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5E80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5EB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5EE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985D06D50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB1D60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB1D30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB28D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2840&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2960&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2990&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2780&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2690&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB26C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB29C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB29F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB23F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2240&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2390&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2270&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB27B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2870&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB28A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB1D90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2660&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB1DC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2930&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79250&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F792E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79220&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79280&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F791F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F78B30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F792B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F798B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F794C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F794F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4050&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC59A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5B20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5FD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6000&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6030&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6060&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6090&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC60C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC60F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6120&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6150&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6180&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC61B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC61E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6210&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5AF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4AD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5A60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4170&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5A00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC49B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4AA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5B80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5BB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5BE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5C10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5C40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5C70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5CA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5CD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5D00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5D30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5D60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5D90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5DC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5DF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5E20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5E50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5E80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5EB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5EE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985D06D50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB1D60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB1D30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB28D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2840&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2960&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2990&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2780&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2690&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB26C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB29C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB29F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB23F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2240&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2390&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2270&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB27B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2870&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB28A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB1D90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2660&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB1DC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2930&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79250&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F792E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79220&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79280&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F791F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F78B30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F792B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F798B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F794C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F794F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4050&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC59A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5B20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5FD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6000&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6030&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6060&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6090&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC60C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC60F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6120&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6150&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6180&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC61B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC61E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6210&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB3D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5AF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4AD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5A60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4170&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5A00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC49B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4AA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5B80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5BB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5BE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5C10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5C40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5C70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5CA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5CD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5D00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5D30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5D60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5D90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5DC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5DF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5E20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5E50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5E80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5EB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5EE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985D06D50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB1D60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB1D30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB28D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2840&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2960&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2990&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2780&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2690&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB26C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB29C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB29F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB23F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2240&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2390&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2270&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB27B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2870&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB28A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB1D90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2660&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB1DC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FB2930&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79250&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F792E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79220&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79280&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F791F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F78B30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F792B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F798B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F794C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F79490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F794F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4B30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4050&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC59A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5B20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5FD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6000&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6030&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6060&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6090&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC60C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC60F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6120&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6150&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6180&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC61B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC61E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6210&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5B50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5970&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC63C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6390&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5F70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5AC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5FA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5F40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC62A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5A30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6420&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6450&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6480&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC64B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC64E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6510&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6540&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6570&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC65A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC65D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6600&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6630&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6660&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6690&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC66C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC66F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6720&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6750&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6780&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC67B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC67E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6810&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6840&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6870&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC68A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC68D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6900&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6930&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6960&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6990&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC69C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC69F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6A20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6A50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6A80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6AB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6AE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6B10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6B40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6B70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6BA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6BD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6C00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6C30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6C60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6C90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6CC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6CF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6D20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6D50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6D80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6DB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6DE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6E10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6E40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6E70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6EA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6ED0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6F00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6F30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6F60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6F90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6FC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6FF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7020&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7050&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC70B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC70E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7170&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC71A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC71D0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5B50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5970&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC63C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6390&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5F70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5AC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5FA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5F40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC62A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5A30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6420&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6450&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6480&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC64B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC64E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6510&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6540&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6570&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC65A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC65D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6600&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6630&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6660&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6690&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC66C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC66F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6720&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6750&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6780&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC67B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC67E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6810&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6840&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6870&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC68A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC68D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6900&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6930&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6960&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6990&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC69C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC69F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6A20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6A50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6A80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6AB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6AE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6B10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6B40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6B70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6BA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6BD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6C00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6C30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6C60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6C90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6CC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6CF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6D20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6D50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6D80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6DB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6DE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6E10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6E40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6E70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6EA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6ED0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6F00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6F30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6F60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6F90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6FC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6FF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7020&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7050&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC70B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC70E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7170&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC71A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC71D0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5B50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5970&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC63C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6390&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5F70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5AC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5FA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5F40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC62A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5A30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6420&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6450&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6480&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC64B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC64E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6510&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6540&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6570&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC65A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC65D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6600&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6630&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6660&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6690&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC66C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC66F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6720&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6750&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6780&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC67B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC67E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6810&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6840&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6870&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC68A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC68D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6900&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6930&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6960&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6990&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC69C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC69F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6A20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6A50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6A80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6AB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6AE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6B10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6B40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6B70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6BA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6BD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6C00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6C30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6C60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6C90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6CC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6CF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6D20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6D50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6D80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6DB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6DE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6E10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6E40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6E70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6EA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6ED0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6F00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6F30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6F60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6F90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6FC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6FF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7020&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7050&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC70B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC70E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7170&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC71A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC71D0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5B50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5970&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC63C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6390&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5F70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5AC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5FA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5F40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC62A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5A30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6420&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6450&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6480&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC64B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC64E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6510&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6540&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6570&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC65A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC65D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6600&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6630&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6660&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6690&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC66C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC66F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6720&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6750&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6780&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC67B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC67E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6810&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6840&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6870&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC68A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC68D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6900&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6930&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6960&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6990&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC69C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC69F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6A20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6A50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6A80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6AB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6AE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6B10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6B40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6B70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6BA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6BD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6C00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6C30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6C60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6C90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6CC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6CF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6D20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6D50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6D80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6DB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6DE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6E10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6E40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6E70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6EA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6ED0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6F00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6F30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6F60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6F90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6FC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6FF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7020&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7050&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC70B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC70E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7170&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC71A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC71D0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5B50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5970&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC63C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6390&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5F70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5AC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5FA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5F40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC62A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5A30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6420&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6450&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6480&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC64B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC64E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6510&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6540&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6570&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC65A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC65D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6600&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6630&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6660&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6690&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC66C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC66F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6720&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6750&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6780&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC67B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC67E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6810&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6840&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6870&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC68A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC68D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6900&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6930&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6960&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6990&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC69C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC69F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6A20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6A50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6A80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6AB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6AE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6B10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6B40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6B70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6BA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6BD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6C00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6C30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6C60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6C90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6CC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6CF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6D20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6D50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6D80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6DB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6DE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6E10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6E40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6E70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6EA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6ED0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6F00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6F30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6F60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6F90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6FC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6FF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7020&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7050&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC70B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC70E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7170&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC71A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC71D0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7230&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC63F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC73B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7380&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7290&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5F10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC59D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6330&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6270&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7410&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7470&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC74A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC74D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7500&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7530&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7560&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7590&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC75C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC75F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7620&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7650&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7680&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC76B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC76E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7770&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC77A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC77D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC78C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC78F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7950&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC79B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC79E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7A40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7A70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7AA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7AD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7B00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7B30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7B60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7C20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7D40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7D70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7DA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7E00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7E90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7EF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7FB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7FE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC72C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC62D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6240&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC72F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7320&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7350&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5A90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC81A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC81D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8200&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7230&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC63F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC73B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7380&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7290&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5F10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC59D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6330&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6270&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7410&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7470&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC74A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC74D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7500&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7530&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7560&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7590&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC75C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC75F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7620&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7650&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7680&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC76B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC76E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7770&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC77A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC77D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC78C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC78F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7950&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC79B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC79E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7A40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7A70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7AA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7AD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7B00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7B30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7B60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7C20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7D40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7D70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7DA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7E00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7E90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7EF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7FB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7FE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC72C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC62D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6240&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC72F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7320&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7350&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5A90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC81A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC81D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8200&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7230&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC63F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC73B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7380&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7290&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5F10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC59D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6330&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6270&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7410&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7470&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC74A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC74D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7500&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7530&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7560&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7590&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC75C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC75F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7620&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7650&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7680&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC76B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC76E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7770&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC77A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC77D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC78C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC78F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7950&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC79B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC79E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7A40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7A70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7AA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7AD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7B00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7B30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7B60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7C20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7D40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7D70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7DA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7E00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7E90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7EF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7FB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7FE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC72C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC62D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6240&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC72F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7320&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7350&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5A90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC81A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC81D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8200&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7230&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC63F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC73B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7380&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC4A40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7290&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5F10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC59D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6330&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6270&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7410&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7470&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC74A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC74D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7500&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7530&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7560&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7590&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC75C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC75F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7620&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7650&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7680&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC76B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC76E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7770&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC77A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC77D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC78C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC78F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7950&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC79B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC79E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7A40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7A70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7AA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7AD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7B00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7B30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7B60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7C20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7D40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7D70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7DA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7E00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7E90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7EF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7FB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7FE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC72C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC62D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC6240&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC72F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7320&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC7350&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC5A90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC81A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC81D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8200&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC80E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x000002398589E0C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC83B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8320&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC80B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC82C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8050&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8170&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8290&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8470&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC84A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC84D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8500&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8530&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8560&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8590&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC85C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC85F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8620&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8650&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8680&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC86B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC86E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8770&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC87A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC87D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC88C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC88F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8950&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC89B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC89E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8A40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8A70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8AA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8AD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8B00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8B30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8B60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8C20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8D40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8D70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8DA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8E00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8E90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8EF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8FB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8FE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9010&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9040&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9070&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC90A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC90D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9100&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9130&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9160&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9190&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC91C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC91F0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC80E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x000002398589E0C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC83B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8320&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC80B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC82C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8050&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8170&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8290&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8470&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC84A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC84D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8500&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8530&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8560&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8590&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC85C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC85F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8620&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8650&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8680&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC86B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC86E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8770&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC87A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC87D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC88C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC88F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8950&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC89B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC89E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8A40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8A70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8AA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8AD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8B00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8B30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8B60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8C20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8D40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8D70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8DA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8E00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8E90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8EF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8FB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8FE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9010&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9040&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9070&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC90A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC90D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9100&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9130&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9160&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9190&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC91C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC91F0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC80E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x000002398589E0C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC83B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8320&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC80B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC82C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8050&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8170&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8290&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8470&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC84A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC84D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8500&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8530&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8560&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8590&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC85C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC85F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8620&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8650&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8680&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC86B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC86E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8770&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC87A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC87D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC88C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC88F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8950&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC89B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC89E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8A40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8A70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8AA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8AD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8B00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8B30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8B60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8C20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8D40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8D70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8DA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8E00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8E90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8EF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8FB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8FE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9010&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9040&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9070&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC90A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC90D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9100&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9130&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9160&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9190&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC91C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC91F0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC80E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x000002398589E0C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC83B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8320&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC80B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC82C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8050&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8170&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8290&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8470&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC84A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC84D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8500&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8530&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8560&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8590&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC85C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC85F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8620&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8650&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8680&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC86B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC86E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8770&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC87A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC87D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC88C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC88F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8950&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC89B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC89E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8A10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8A40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8A70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8AA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8AD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8B00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8B30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8B60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8B90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8BC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8BF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8C20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8C50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8C80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8CB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8CE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8D10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8D40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8D70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8DA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8DD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8E00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8E30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8E60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8E90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8EC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8EF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8F20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8F50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8F80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8FB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8FE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9010&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9040&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9070&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC90A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC90D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9100&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9130&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9160&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9190&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC91C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC91F0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8410&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EBD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC93A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8380&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9310&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC92B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8260&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8230&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8350&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9430&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC94C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC94F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9580&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC95B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC95E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9610&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9640&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9670&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC96A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC96D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9700&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9760&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9790&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC97C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC97F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9820&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9850&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9880&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC98B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC98E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9910&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9940&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9970&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC99A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC99D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9A00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9A30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9A60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9A90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9AC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9AF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9B20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9B50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9B80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9BB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9BE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9C10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9C40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9C70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9CA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9CD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9D00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9D30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9D60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9D90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9DC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9DF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9E20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9E50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9E80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9EB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9EE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9F10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9F40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9F70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9FA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9FD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA000&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA030&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA060&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA090&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA0C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA0F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA120&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA150&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA180&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA1B0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8410&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985F1EBD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC93A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8380&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9310&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC92B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8260&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8230&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8350&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9430&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9460&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9490&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC94C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC94F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9520&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9550&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9580&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC95B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC95E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9610&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9640&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9670&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC96A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC96D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9700&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9730&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9760&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9790&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC97C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC97F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9820&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9850&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9880&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC98B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC98E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9910&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9940&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9970&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC99A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC99D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9A00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9A30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9A60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9A90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9AC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9AF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9B20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9B50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9B80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9BB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9BE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9C10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9C40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9C70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9CA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9CD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9D00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9D30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9D60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9D90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9DC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9DF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9E20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9E50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9E80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9EB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9EE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9F10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9F40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9F70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9FA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9FD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA000&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA030&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA060&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA090&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA0C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA0F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA120&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA150&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA180&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA1B0&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA210&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9400&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA390&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA360&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9340&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA270&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9370&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC93D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC92E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC82F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA3F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA420&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA450&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA480&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA4B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA4E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA510&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA540&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA570&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA5A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA5D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA600&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA630&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA660&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA690&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA6C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA6F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA720&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA750&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA780&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA7B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA7E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA810&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA840&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA870&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA8A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA8D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA900&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA930&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA960&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA990&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA9C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA9F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAA20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAA50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAA80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAAB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAAE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAB10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAB40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAB70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCABA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCABD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAC00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAC30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAC60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAC90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCACC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCACF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAD20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAD50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAD80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCADB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCADE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAE10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAE40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAE70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAEA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAED0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAF00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAF30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAF60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAF90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAFC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAFF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB020&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB050&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB0B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB0E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB170&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA210&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9400&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA390&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA360&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9340&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA270&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9370&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC93D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC92E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC82F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA3F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA420&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA450&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA480&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA4B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA4E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA510&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA540&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA570&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA5A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA5D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA600&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA630&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA660&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA690&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA6C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA6F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA720&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA750&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA780&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA7B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA7E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA810&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA840&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA870&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA8A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA8D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA900&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA930&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA960&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA990&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA9C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA9F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAA20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAA50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAA80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAAB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAAE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAB10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAB40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAB70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCABA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCABD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAC00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAC30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAC60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAC90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCACC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCACF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAD20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAD50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAD80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCADB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCADE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAE10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAE40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAE70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAEA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAED0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAF00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAF30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAF60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAF90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAFC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCAFF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB020&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB050&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB0B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB0E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB110&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB140&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB170&gt;]}</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>{'distribution_type': 'deterministic', 'mean': 5.0}</t>
+          <t>{'distribution_type': 'cdf_curve', 'fragility_values': [&lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB1D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA3C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB350&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB320&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA330&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB230&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA2A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA300&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC83E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA1E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB3B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB3E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB410&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB440&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB470&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB4A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB4D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB500&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB530&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB560&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB590&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB5C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB5F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB620&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB650&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB680&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB6B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB6E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB710&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB740&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB770&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB7A0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB7D0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB800&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB830&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB860&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB890&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB8C0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB8F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB920&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB950&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB980&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB9B0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB9E0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBA10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBA40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBA70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBAA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBAD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBB00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBB30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBB60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBB90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBBC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBBF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBC20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBC50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBC80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBCB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBCE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBD10&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBD40&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBD70&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBDA0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBDD0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBE00&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBE30&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBE60&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBE90&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBEC0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBEF0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBF20&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBF50&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBF80&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBFB0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCBFE0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB2F0&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC9250&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FC8080&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCA240&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB260&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB290&gt;, &lt;probabilistic_library.statistic.FragilityValue object at 0x0000023985FCB2C0&gt;]}</t>
         </is>
       </c>
     </row>
